--- a/data/trans_dic/IP12B$otros-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$otros-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por otros síntomas o dolor</t>
+          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,55</t>
+          <t>0,0; 34,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,27</t>
+          <t>0,0; 19,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,83; 60,04</t>
+          <t>15,5; 60,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,27</t>
+          <t>0,0; 33,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,58</t>
+          <t>0,0; 50,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,46; 40,34</t>
+          <t>11,04; 38,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,59</t>
+          <t>0,0; 16,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,65</t>
+          <t>0,0; 22,63</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,34; 34,42</t>
+          <t>4,37; 37,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 31,47</t>
+          <t>3,7; 33,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,59; 44,79</t>
+          <t>12,78; 45,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 36,8</t>
+          <t>4,21; 37,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,48</t>
+          <t>0,0; 26,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,22</t>
+          <t>0,0; 26,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,75; 28,02</t>
+          <t>6,61; 29,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,94; 23,4</t>
+          <t>4,08; 22,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 28,52</t>
+          <t>8,79; 30,12</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,76</t>
+          <t>0,0; 24,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,76; 59,25</t>
+          <t>12,99; 63,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,9</t>
+          <t>0,0; 32,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,93</t>
+          <t>0,0; 39,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,82</t>
+          <t>0,0; 22,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,88; 36,48</t>
+          <t>5,06; 39,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,24</t>
+          <t>0,0; 18,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 28,95</t>
+          <t>6,43; 29,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 26,59</t>
+          <t>4,68; 25,55</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,83</t>
+          <t>0,0; 31,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,17</t>
+          <t>0,0; 32,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,16</t>
+          <t>0,0; 33,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 30,68</t>
+          <t>3,44; 28,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,54</t>
+          <t>0,0; 37,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,6</t>
+          <t>0,0; 15,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 24,38</t>
+          <t>5,06; 23,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 27,06</t>
+          <t>2,99; 25,71</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 17,89</t>
+          <t>3,06; 17,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,5; 22,26</t>
+          <t>7,37; 22,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,56; 22,1</t>
+          <t>7,02; 23,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,09; 27,83</t>
+          <t>10,1; 26,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,05; 15,43</t>
+          <t>3,88; 15,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,4; 20,65</t>
+          <t>5,61; 21,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,27; 19,26</t>
+          <t>8,17; 19,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,88; 16,03</t>
+          <t>7,11; 16,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,72; 18,67</t>
+          <t>8,04; 18,16</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1354</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4153</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5508</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4247</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3323</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1828; 7075</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3426</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3624</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2653; 9271</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4568</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3618</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1786</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2898</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5241</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2644</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4430</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3551</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>6030</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>529; 4540</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>710; 6469</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2591; 9265</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>680; 5979</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3687</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4149</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1865; 8210</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1359; 7424</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3150; 10791</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3099</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2752</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1291</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4286</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3396</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3134</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1224; 5976</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3767</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3267</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4019</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>806; 6299</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3915</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1771; 8230</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1290; 7036</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1654</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1516</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2796</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4449</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2727</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4918</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4678</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3508</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>727; 6073</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3464</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2730</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1853; 8564</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>706; 6076</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3772</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8301</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8106</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5429</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>11878</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>13589</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>12830</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1344; 7551</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4517; 13485</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3871; 12972</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4716; 12604</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2467; 9817</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2686; 10056</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7404; 17859</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>8877; 20553</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>8280; 18700</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$otros-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$otros-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,69</t>
+          <t>0,0; 32,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,38</t>
+          <t>0,0; 16,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,32 +693,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,5; 60,03</t>
+          <t>15,98; 59,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,56</t>
+          <t>0,0; 31,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,91</t>
+          <t>0,0; 43,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,04; 38,58</t>
+          <t>11,42; 38,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,7</t>
+          <t>0,0; 15,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,63</t>
+          <t>0,0; 22,38</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 37,54</t>
+          <t>4,38; 38,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 33,72</t>
+          <t>3,53; 34,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,78; 45,7</t>
+          <t>11,94; 43,47</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 37,03</t>
+          <t>4,19; 33,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,1</t>
+          <t>0,0; 21,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,67</t>
+          <t>0,0; 24,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,61; 29,07</t>
+          <t>6,58; 29,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 22,29</t>
+          <t>4,01; 24,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,79; 30,12</t>
+          <t>8,91; 28,84</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,68</t>
+          <t>0,0; 20,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,99; 63,46</t>
+          <t>12,85; 59,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,49</t>
+          <t>0,0; 28,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,46</t>
+          <t>0,0; 38,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,18</t>
+          <t>0,0; 20,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 39,51</t>
+          <t>4,17; 35,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,66</t>
+          <t>0,0; 18,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 29,89</t>
+          <t>6,96; 29,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,68; 25,55</t>
+          <t>4,71; 25,81</t>
         </is>
       </c>
     </row>
@@ -1013,42 +1013,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,62</t>
+          <t>0,0; 30,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,52</t>
+          <t>0,0; 30,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,43</t>
+          <t>0,0; 30,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 28,77</t>
+          <t>3,34; 29,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,48</t>
+          <t>0,0; 42,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,74</t>
+          <t>0,0; 19,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 23,36</t>
+          <t>5,65; 24,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,99; 25,71</t>
+          <t>3,03; 25,86</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,06; 17,21</t>
+          <t>3,14; 17,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,37; 22,0</t>
+          <t>6,94; 21,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,02; 23,53</t>
+          <t>7,77; 22,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,1; 26,98</t>
+          <t>9,46; 28,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 15,44</t>
+          <t>3,64; 15,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,61; 21,01</t>
+          <t>5,23; 20,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,17; 19,71</t>
+          <t>8,52; 19,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,11; 16,46</t>
+          <t>7,0; 16,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,04; 18,16</t>
+          <t>7,74; 18,01</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por otros síntomas o dolor (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4247</t>
+          <t>0; 3991</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3323</t>
+          <t>0; 2761</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1432,32 +1432,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1828; 7075</t>
+          <t>1883; 7015</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3426</t>
+          <t>0; 3266</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3624</t>
+          <t>0; 3067</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2653; 9271</t>
+          <t>2744; 9221</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4568</t>
+          <t>0; 4125</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3618</t>
+          <t>0; 3579</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>529; 4540</t>
+          <t>529; 4641</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>710; 6469</t>
+          <t>677; 6527</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2591; 9265</t>
+          <t>2420; 8813</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>680; 5979</t>
+          <t>677; 5458</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3687</t>
+          <t>0; 3038</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4149</t>
+          <t>0; 3872</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1865; 8210</t>
+          <t>1858; 8410</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1359; 7424</t>
+          <t>1337; 8079</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3150; 10791</t>
+          <t>3192; 10334</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3134</t>
+          <t>0; 2626</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1224; 5976</t>
+          <t>1210; 5594</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3767</t>
+          <t>0; 3308</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3267</t>
+          <t>0; 3211</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4019</t>
+          <t>0; 3723</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>806; 6299</t>
+          <t>664; 5600</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3915</t>
+          <t>0; 3973</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1771; 8230</t>
+          <t>1917; 8191</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1290; 7036</t>
+          <t>1296; 7106</t>
         </is>
       </c>
     </row>
@@ -1911,42 +1911,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4918</t>
+          <t>0; 4690</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4678</t>
+          <t>0; 4446</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3508</t>
+          <t>0; 3245</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>727; 6073</t>
+          <t>705; 6313</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3464</t>
+          <t>0; 3930</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2730</t>
+          <t>0; 3376</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1853; 8564</t>
+          <t>2070; 8987</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>706; 6076</t>
+          <t>715; 6111</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1344; 7551</t>
+          <t>1378; 7814</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4517; 13485</t>
+          <t>4255; 13414</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3871; 12972</t>
+          <t>4281; 12226</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4716; 12604</t>
+          <t>4420; 13198</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2467; 9817</t>
+          <t>2311; 9887</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2686; 10056</t>
+          <t>2505; 9701</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7404; 17859</t>
+          <t>7715; 17813</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8877; 20553</t>
+          <t>8735; 20341</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8280; 18700</t>
+          <t>7974; 18549</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$otros-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$otros-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>35,24%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9,51%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>11,06%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3,79%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>35,24%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,6</t>
+          <t>15,83; 60,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,11</t>
+          <t>0,0; 34,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 42,58</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 34,55</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 19,27</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15,98; 59,51</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 31,98</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 43,08</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,42; 38,37</t>
+          <t>11,46; 40,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,08</t>
+          <t>0,0; 16,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,38</t>
+          <t>0,0; 21,65</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>16,38%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>14,77%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>15,11%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>25,85%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>16,38%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 38,37</t>
+          <t>4,19; 36,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 34,02</t>
+          <t>0,0; 21,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,94; 43,47</t>
+          <t>0,0; 20,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 33,8</t>
+          <t>4,34; 34,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,51</t>
+          <t>3,69; 31,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,89</t>
+          <t>12,59; 44,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,58; 29,78</t>
+          <t>6,75; 28,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,01; 24,26</t>
+          <t>3,94; 23,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,91; 28,84</t>
+          <t>7,5; 28,52</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,55%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17,26%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>4,98%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>32,91%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5,56%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,55%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,68</t>
+          <t>0,0; 39,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,85; 59,41</t>
+          <t>0,0; 19,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,54</t>
+          <t>4,88; 36,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,79</t>
+          <t>0,0; 24,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,55</t>
+          <t>12,76; 59,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 35,12</t>
+          <t>0,0; 29,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,94</t>
+          <t>0,0; 19,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,96; 29,75</t>
+          <t>6,73; 28,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,71; 25,81</t>
+          <t>4,61; 26,59</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13,11%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>10,63%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10,53%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,25%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 31,16</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3,38; 30,68</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 37,54</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 30,16</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 30,91</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 30,92</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,34; 29,91</t>
+          <t>0,0; 31,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,54</t>
+          <t>0,0; 30,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,47</t>
+          <t>0,0; 18,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 24,52</t>
+          <t>5,5; 24,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 25,86</t>
+          <t>2,96; 27,06</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17,36%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8,32%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11,35%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>8,6%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>13,54%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>13,43%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17,36%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,32%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,14; 17,81</t>
+          <t>10,09; 27,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,94; 21,89</t>
+          <t>4,05; 15,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,77; 22,18</t>
+          <t>5,4; 20,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,46; 28,26</t>
+          <t>4,07; 17,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 15,56</t>
+          <t>7,5; 22,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 20,27</t>
+          <t>7,56; 22,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,52; 19,67</t>
+          <t>8,27; 19,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,0; 16,29</t>
+          <t>6,88; 16,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,74; 18,01</t>
+          <t>7,72; 18,67</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4153</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1354</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>650</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4153</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3991</t>
+          <t>1866; 7077</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2761</t>
+          <t>0; 3499</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>0; 3031</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4230</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3303</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1883; 7015</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3266</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3067</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2744; 9221</t>
+          <t>2754; 9693</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4125</t>
+          <t>0; 4537</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3579</t>
+          <t>0; 3461</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2644</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1786</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2898</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5241</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2644</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>529; 4641</t>
+          <t>676; 5941</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>677; 6527</t>
+          <t>0; 3034</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2420; 8813</t>
+          <t>0; 3146</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>677; 5458</t>
+          <t>525; 4163</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3038</t>
+          <t>707; 6037</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3872</t>
+          <t>2552; 9081</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1858; 8410</t>
+          <t>1906; 7913</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1337; 8079</t>
+          <t>1313; 7794</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3192; 10334</t>
+          <t>2688; 10219</t>
         </is>
       </c>
     </row>
@@ -1642,27 +1642,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2752</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>3099</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>645</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1187</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2752</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2626</t>
+          <t>0; 3306</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1210; 5594</t>
+          <t>0; 3591</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3308</t>
+          <t>778; 5815</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3211</t>
+          <t>0; 3143</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3723</t>
+          <t>1202; 5579</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>664; 5600</t>
+          <t>0; 3467</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3973</t>
+          <t>0; 4035</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1917; 8191</t>
+          <t>1854; 7970</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1296; 7106</t>
+          <t>1269; 7322</t>
         </is>
       </c>
     </row>
@@ -1800,27 +1800,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2796</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1654</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1516</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2796</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1211</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>0; 3271</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>712; 6476</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3469</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>0; 4690</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0; 4446</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0; 3245</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>705; 6313</t>
+          <t>0; 4950</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3930</t>
+          <t>0; 4341</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3376</t>
+          <t>0; 3226</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2070; 8987</t>
+          <t>2015; 8936</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>715; 6111</t>
+          <t>700; 6393</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>8106</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5429</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>3772</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>8301</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>7401</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8106</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>5288</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5429</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1378; 7814</t>
+          <t>4714; 12997</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4255; 13414</t>
+          <t>2571; 9810</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4281; 12226</t>
+          <t>2585; 9882</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4420; 13198</t>
+          <t>1786; 7849</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2311; 9887</t>
+          <t>4596; 13643</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2505; 9701</t>
+          <t>4168; 12183</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7715; 17813</t>
+          <t>7496; 17444</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8735; 20341</t>
+          <t>8587; 20013</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7974; 18549</t>
+          <t>7951; 19226</t>
         </is>
       </c>
     </row>
